--- a/题库/PY程序设计实验-模拟题3.xlsx
+++ b/题库/PY程序设计实验-模拟题3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="11950" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -179,8 +179,7 @@
 y = int(input("【从键盘输入另一个数:y】"))
 z = int(input("【从键盘输入另一个数:z】"))
 m = max(x, y, z)
-n = min(x, y, z)
-print("最大数: %d, 最小数: %d" % (m, n))</t>
+n = min(x, y, z)</t>
   </si>
   <si>
     <t>Prog3.4.py</t>
@@ -189,29 +188,26 @@
     <t>x = int(input("【从键盘输入一个数:x】"))
 y = int(input("【从键盘输入另一个数:y】"))
 t = x // y
-d = x % y
-print("x和y 商：%d，余数：%d" % (t, d))</t>
+d = x % y</t>
   </si>
   <si>
     <t>Prog3.5.py</t>
   </si>
   <si>
-    <t>x = int(input("【从键盘输入一个数：】"))
-y = int(input("【从键盘输入另一个数：】"))
-s = x + y
-b = x - y
-p = x * y
-print("x和y和：%d, 差：%d, 积：%d" % (s, b, p))</t>
+    <t>x=int(input("【从键盘输入一个数x：】 "))
+y=int(input("【从键盘输入另一个数y：】 "))
+s=x+y
+b=x-y
+p=x*y</t>
   </si>
   <si>
     <t>Prog3.6.py</t>
   </si>
   <si>
     <t>import math
-r = float(input("【圆的半径：】"))
-c = 2 * math.pi * r
-s = math.pi * r * r
-print("圆的周长: %.2f, 圆的面积: %.2f" % (c, s))</t>
+r=float(input("【圆的半径：】 "))
+c=2*math.pi*r
+s=math.pi*r*r</t>
   </si>
   <si>
     <t>Prog3.7.py</t>
@@ -220,8 +216,7 @@
     <t>chinese = float(input("【从键盘输入语文成绩：】"))
 math = float(input("【从键盘输入数学成绩：】"))
 sum = chinese + math
-avg = sum / 2
-print("总成绩：%.1f，平均成绩：%.1f" % (sum, avg))</t>
+avg = sum / 2</t>
   </si>
   <si>
     <t>Prog3.8.py</t>
@@ -229,15 +224,13 @@
   <si>
     <t>dad = int(input("【从键盘输入爸爸年龄：】"))
 son = int(input("【从键盘输入儿子年龄：】"))
-diff = dad - son
-print("父子年龄差距：", diff)</t>
+diff = dad - son</t>
   </si>
   <si>
     <t>Prog3.9.py</t>
   </si>
   <si>
-    <t>def fun(n, a):
-    if n == 1:
+    <t xml:space="preserve">    if n == 1:
         return a
     else:
         r = fun(n-1, a) * 10 + a
@@ -247,8 +240,7 @@
     <t>Prog3.10.py</t>
   </si>
   <si>
-    <t>def fun(s):
-    if s[0] == s[-1] and s[1] == s[-2]:
+    <t xml:space="preserve">    if s[0] == s[-1] and s[1] == s[-2]:
         return True
     else:
         return False</t>
